--- a/ui/public/sample/sample-toanha.xlsx
+++ b/ui/public/sample/sample-toanha.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\vlute\kiemketaisan\ui\public\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF5AD6A-5A18-4C54-A338-5D77EEA70EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D5CB93-7373-48D2-A930-D5D9A97E5F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C95F5611-DAB2-41DA-80F8-6441986022DE}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
   <si>
     <t>Mã tòa nhà</t>
   </si>
@@ -92,29 +92,209 @@
     <t>Ngày chuyển trạng thái</t>
   </si>
   <si>
-    <t>TN_01</t>
-  </si>
-  <si>
-    <t>Tòa nhà 01</t>
-  </si>
-  <si>
-    <t>Sở hữu</t>
-  </si>
-  <si>
-    <t>Trường Đại học 1</t>
-  </si>
-  <si>
-    <t>Ngừng sử dụng</t>
-  </si>
-  <si>
-    <t>14/01/2020</t>
+    <t>Place</t>
+  </si>
+  <si>
+    <t>TN_C</t>
+  </si>
+  <si>
+    <t>Nhà học 11 tầng (Nhà C)</t>
+  </si>
+  <si>
+    <t>TN_N</t>
+  </si>
+  <si>
+    <t>Khu nhà học cầu nối Nhà C - Nhà B</t>
+  </si>
+  <si>
+    <t>TN_B</t>
+  </si>
+  <si>
+    <t>Nhà học 05 tầng (Nhà B)</t>
+  </si>
+  <si>
+    <t>TN_A</t>
+  </si>
+  <si>
+    <t>Nhà học 03 tầng (Nhà A)</t>
+  </si>
+  <si>
+    <t>TN_G</t>
+  </si>
+  <si>
+    <t>Khu nhà xưởng thực hành động lực</t>
+  </si>
+  <si>
+    <t>TN_D</t>
+  </si>
+  <si>
+    <t>Nhà học 03 tầng (Nhà D)</t>
+  </si>
+  <si>
+    <t>TN_E</t>
+  </si>
+  <si>
+    <t>Nhà học 02 tầng (Nhà E)</t>
+  </si>
+  <si>
+    <t>TN_F</t>
+  </si>
+  <si>
+    <t>Nhà học 02 tầng (Nhà F)</t>
+  </si>
+  <si>
+    <t>TN_TTOTO</t>
+  </si>
+  <si>
+    <t>Xưởng thực hành công nghệ ô tô 03</t>
+  </si>
+  <si>
+    <t>TN_TTCNSH</t>
+  </si>
+  <si>
+    <t>Khu thực hành công nghệ sinh học 01</t>
+  </si>
+  <si>
+    <t>TN_BXTY</t>
+  </si>
+  <si>
+    <t>Bệnh xá thú y</t>
+  </si>
+  <si>
+    <t>TN_BV</t>
+  </si>
+  <si>
+    <t>Trung tâm tuyển sinh và nhà bảo vệ</t>
+  </si>
+  <si>
+    <t>TN_NXGV</t>
+  </si>
+  <si>
+    <t>Khu nhà để xe giáo viên</t>
+  </si>
+  <si>
+    <t>TN_CV</t>
+  </si>
+  <si>
+    <t>Nhà công vụ</t>
+  </si>
+  <si>
+    <t>TN_DVDT</t>
+  </si>
+  <si>
+    <t>Khu dịch vụ điện tử - điện lạnh</t>
+  </si>
+  <si>
+    <t>TN_THCK1</t>
+  </si>
+  <si>
+    <t>Xưởng thực hành cơ khí - Kỹ thuật hàn 1 + 2</t>
+  </si>
+  <si>
+    <t>TN_THCK</t>
+  </si>
+  <si>
+    <t>Xưởng thực hành cơ khí – Trung tâm công nghệ cao 01</t>
+  </si>
+  <si>
+    <t>TN_NMSH</t>
+  </si>
+  <si>
+    <t>Khu nhà màng thực hành công nghệ sinh học</t>
+  </si>
+  <si>
+    <t>TN_K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khu thực hành thú y - Bệnh xá, khu nuôi nhốt gia súc gia cầm </t>
+  </si>
+  <si>
+    <t>TN_KVTTH</t>
+  </si>
+  <si>
+    <t>Kho vật tư tổng hợp</t>
+  </si>
+  <si>
+    <t>TN_THDLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khu học tập tổng hợp ngành du lịch </t>
+  </si>
+  <si>
+    <t>TN_THXD</t>
+  </si>
+  <si>
+    <t>Khu thực hành ngành xây dựng</t>
+  </si>
+  <si>
+    <t>TN_KLT</t>
+  </si>
+  <si>
+    <t>Kho lưu trữ tài liệu đào tạo, tuyển sinh, NCKH, …</t>
+  </si>
+  <si>
+    <t>TN_LTDQP</t>
+  </si>
+  <si>
+    <t>Khu luyện tập thể dục – quốc phòng</t>
+  </si>
+  <si>
+    <t>TN_THDLB</t>
+  </si>
+  <si>
+    <t>TT thực hành du lịch - nhà B</t>
+  </si>
+  <si>
+    <t>TN_TTNLD</t>
+  </si>
+  <si>
+    <t>Trung tâm năng lượng điện</t>
+  </si>
+  <si>
+    <t>TN_NTD</t>
+  </si>
+  <si>
+    <t>Nhà thi đấu đa năng</t>
+  </si>
+  <si>
+    <t>TN_NCKH</t>
+  </si>
+  <si>
+    <t>Nhà nghiên cứu khoa học 9 tầng</t>
+  </si>
+  <si>
+    <t>XOTO</t>
+  </si>
+  <si>
+    <t>Xưởng ô tô nhà tiền chế</t>
+  </si>
+  <si>
+    <t>NCV2</t>
+  </si>
+  <si>
+    <t>Nhà công vụ 2</t>
+  </si>
+  <si>
+    <t>TN_KTXA</t>
+  </si>
+  <si>
+    <t>Ký túc xá 05 tầng</t>
+  </si>
+  <si>
+    <t>TN_KTXB</t>
+  </si>
+  <si>
+    <t>Ký túc xá 6 tầng</t>
+  </si>
+  <si>
+    <t>Trường Đại học Sư phạm Kỹ thuật Vĩnh Long</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +334,24 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -181,7 +379,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -219,11 +417,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,19 +469,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -255,10 +478,25 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,7 +831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FB29F12-85DA-43D7-8853-B06EAA8DF6CF}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
@@ -607,7 +845,7 @@
     <col min="10" max="10" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="75" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="75" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -638,461 +876,994 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4">
-        <v>1200</v>
-      </c>
-      <c r="D2" s="4">
-        <v>5000</v>
-      </c>
-      <c r="E2" s="4">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="B2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="13">
+        <v>1024</v>
+      </c>
+      <c r="D2" s="13">
+        <v>13312</v>
+      </c>
+      <c r="E2" s="13">
+        <v>11</v>
+      </c>
+      <c r="F2" s="13">
+        <v>2014</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="13">
+        <v>177.5</v>
+      </c>
+      <c r="D3" s="13">
+        <v>710</v>
+      </c>
+      <c r="E3" s="13">
+        <v>5</v>
+      </c>
+      <c r="F3" s="13">
+        <v>2019</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="13">
+        <v>1102</v>
+      </c>
+      <c r="D4" s="13">
+        <v>5810</v>
+      </c>
+      <c r="E4" s="13">
+        <v>5</v>
+      </c>
+      <c r="F4" s="13">
+        <v>2010</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="13">
+        <v>1070.9000000000001</v>
+      </c>
+      <c r="D5" s="13">
+        <v>4079</v>
+      </c>
+      <c r="E5" s="13">
+        <v>3</v>
+      </c>
+      <c r="F5" s="13">
+        <v>1960</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="13">
+        <v>3432</v>
+      </c>
+      <c r="D6" s="13">
+        <v>3432</v>
+      </c>
+      <c r="E6" s="13">
+        <v>1</v>
+      </c>
+      <c r="F6" s="13">
+        <v>1960</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="13">
+        <v>341</v>
+      </c>
+      <c r="D7" s="13">
+        <v>1023</v>
+      </c>
+      <c r="E7" s="13">
+        <v>3</v>
+      </c>
+      <c r="F7" s="13">
+        <v>1984</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="13">
+        <v>484</v>
+      </c>
+      <c r="D8" s="13">
+        <v>968</v>
+      </c>
+      <c r="E8" s="13">
+        <v>2</v>
+      </c>
+      <c r="F8" s="13">
+        <v>1984</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="13">
+        <v>323.5</v>
+      </c>
+      <c r="D9" s="13">
+        <v>647</v>
+      </c>
+      <c r="E9" s="13">
+        <v>2</v>
+      </c>
+      <c r="F9" s="13">
+        <v>1977</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="13">
+        <v>300</v>
+      </c>
+      <c r="D10" s="13">
+        <v>300</v>
+      </c>
+      <c r="E10" s="13">
+        <v>1</v>
+      </c>
+      <c r="F10" s="13">
+        <v>2018</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="13">
+        <v>180</v>
+      </c>
+      <c r="D11" s="13">
+        <v>180</v>
+      </c>
+      <c r="E11" s="13">
+        <v>1</v>
+      </c>
+      <c r="F11" s="13">
+        <v>2018</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="13">
+        <v>160</v>
+      </c>
+      <c r="D12" s="13">
+        <v>160</v>
+      </c>
+      <c r="E12" s="13">
+        <v>1</v>
+      </c>
+      <c r="F12" s="13">
+        <v>1980</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="13">
+        <v>85.8</v>
+      </c>
+      <c r="D13" s="13">
+        <v>85.8</v>
+      </c>
+      <c r="E13" s="13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13">
+        <v>2025</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="13">
+        <v>251</v>
+      </c>
+      <c r="D14" s="13">
+        <v>251</v>
+      </c>
+      <c r="E14" s="13">
+        <v>1</v>
+      </c>
+      <c r="F14" s="13">
+        <v>1976</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="13">
+        <v>32</v>
+      </c>
+      <c r="D15" s="13">
+        <v>32</v>
+      </c>
+      <c r="E15" s="13">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1986</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="13">
+        <v>35</v>
+      </c>
+      <c r="D16" s="13">
+        <v>35</v>
+      </c>
+      <c r="E16" s="13">
+        <v>1</v>
+      </c>
+      <c r="F16" s="13">
+        <v>2018</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="13">
+        <v>372</v>
+      </c>
+      <c r="D17" s="13">
+        <v>372</v>
+      </c>
+      <c r="E17" s="13">
+        <v>1</v>
+      </c>
+      <c r="F17" s="13">
+        <v>2016</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="13">
+        <v>540</v>
+      </c>
+      <c r="D18" s="13">
+        <v>540</v>
+      </c>
+      <c r="E18" s="13">
+        <v>1</v>
+      </c>
+      <c r="F18" s="13">
+        <v>2022</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="13">
+        <v>200</v>
+      </c>
+      <c r="D19" s="13">
+        <v>200</v>
+      </c>
+      <c r="E19" s="13">
+        <v>1</v>
+      </c>
+      <c r="F19" s="13">
+        <v>2018</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="13">
+        <v>210</v>
+      </c>
+      <c r="D20" s="13">
+        <v>210</v>
+      </c>
+      <c r="E20" s="13">
+        <v>1</v>
+      </c>
+      <c r="F20" s="13">
+        <v>2018</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="13">
+        <v>200</v>
+      </c>
+      <c r="D21" s="13">
+        <v>200</v>
+      </c>
+      <c r="E21" s="13">
+        <v>1</v>
+      </c>
+      <c r="F21" s="13">
+        <v>2021</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="J21" s="11"/>
+      <c r="K21" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="13">
+        <v>1000</v>
+      </c>
+      <c r="D22" s="13">
+        <v>1000</v>
+      </c>
+      <c r="E22" s="13">
+        <v>1</v>
+      </c>
+      <c r="F22" s="13">
+        <v>2022</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="13">
+        <v>150</v>
+      </c>
+      <c r="D23" s="13">
+        <v>150</v>
+      </c>
+      <c r="E23" s="13">
+        <v>1</v>
+      </c>
+      <c r="F23" s="13">
         <v>2024</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="11"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-    </row>
-    <row r="11" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-    </row>
-    <row r="20" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-    </row>
-    <row r="21" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-    </row>
-    <row r="22" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-    </row>
-    <row r="24" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
-      <c r="J24" s="12"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-    </row>
-    <row r="27" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-    </row>
-    <row r="28" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-    </row>
-    <row r="29" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-    </row>
-    <row r="30" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-    </row>
-    <row r="31" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-    </row>
-    <row r="32" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-    </row>
-    <row r="33" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-    </row>
-    <row r="34" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-    </row>
-    <row r="35" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-    </row>
-    <row r="36" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="13">
+        <v>84</v>
+      </c>
+      <c r="D24" s="13">
+        <v>84</v>
+      </c>
+      <c r="E24" s="13">
+        <v>1</v>
+      </c>
+      <c r="F24" s="13">
+        <v>2006</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="13">
+        <v>1000</v>
+      </c>
+      <c r="D25" s="13">
+        <v>1000</v>
+      </c>
+      <c r="E25" s="13">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13">
+        <v>2023</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C26" s="13">
+        <v>84</v>
+      </c>
+      <c r="D26" s="13">
+        <v>84</v>
+      </c>
+      <c r="E26" s="13">
+        <v>1</v>
+      </c>
+      <c r="F26" s="13">
+        <v>2022</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="7"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C27" s="13">
+        <v>500</v>
+      </c>
+      <c r="D27" s="13">
+        <v>500</v>
+      </c>
+      <c r="E27" s="13">
+        <v>1</v>
+      </c>
+      <c r="F27" s="13">
+        <v>2024</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I27" s="7"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="13">
+        <v>1740</v>
+      </c>
+      <c r="D28" s="13">
+        <v>1740</v>
+      </c>
+      <c r="E28" s="13">
+        <v>1</v>
+      </c>
+      <c r="F28" s="13">
+        <v>2023</v>
+      </c>
+      <c r="G28" s="3"/>
+      <c r="H28" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C29" s="13">
+        <v>1741</v>
+      </c>
+      <c r="D29" s="13">
+        <v>15669</v>
+      </c>
+      <c r="E29" s="13">
+        <v>9</v>
+      </c>
+      <c r="F29" s="13">
+        <v>2025</v>
+      </c>
+      <c r="G29" s="3"/>
+      <c r="H29" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="13">
+        <v>200</v>
+      </c>
+      <c r="D30" s="13">
+        <v>200</v>
+      </c>
+      <c r="E30" s="13">
+        <v>1</v>
+      </c>
+      <c r="F30" s="13">
+        <v>2019</v>
+      </c>
+      <c r="G30" s="3"/>
+      <c r="H30" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="13">
+        <v>60.5</v>
+      </c>
+      <c r="D31" s="13">
+        <v>60.5</v>
+      </c>
+      <c r="E31" s="13">
+        <v>1</v>
+      </c>
+      <c r="F31" s="13">
+        <v>1986</v>
+      </c>
+      <c r="G31" s="3"/>
+      <c r="H31" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="13">
+        <v>611</v>
+      </c>
+      <c r="D32" s="13">
+        <v>3056</v>
+      </c>
+      <c r="E32" s="13">
+        <v>5</v>
+      </c>
+      <c r="F32" s="13">
+        <v>2005</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I32" s="7"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="13">
+        <v>966</v>
+      </c>
+      <c r="D33" s="13">
+        <v>6000</v>
+      </c>
+      <c r="E33" s="13">
+        <v>6</v>
+      </c>
+      <c r="F33" s="13">
+        <v>2017</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I33" s="7"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="12"/>
+    </row>
+    <row r="35" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="12"/>
+    </row>
+    <row r="36" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="12"/>
+    </row>
+    <row r="37" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="12"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>